--- a/demo2/demo2-input_2.xlsx
+++ b/demo2/demo2-input_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VEA Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VEA Config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -323,7 +323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -345,11 +345,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -493,6 +537,8 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4428,6 +4474,19 @@
 ▶ Başlamak için ekrana tıklayın</t>
         </is>
       </c>
+      <c r="C74" s="53" t="n"/>
+      <c r="D74" s="53" t="n"/>
+      <c r="E74" s="53" t="n"/>
+      <c r="F74" s="53" t="n"/>
+      <c r="G74" s="53" t="n"/>
+      <c r="H74" s="53" t="n"/>
+      <c r="I74" s="53" t="n"/>
+      <c r="J74" s="53" t="n"/>
+      <c r="K74" s="53" t="n"/>
+      <c r="L74" s="53" t="n"/>
+      <c r="M74" s="53" t="n"/>
+      <c r="N74" s="53" t="n"/>
+      <c r="O74" s="54" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="32" t="inlineStr">
@@ -5247,13 +5306,26 @@
       </c>
       <c r="B89" s="36" t="inlineStr">
         <is>
-          <t>Proje: Nova Residence
-Geliştirici: VEA Development
-Konum: İstanbul, Türkiye
-Teslim: Q4 2026
-Toplam Ünite: 240</t>
-        </is>
-      </c>
+          <t>**Proje:** Nova Residence
+**Geliştirici:** VEA Development
+**Konum:** İstanbul, Türkiye
+**Teslim:** Q4 2026
+**Toplam Ünite:** 240</t>
+        </is>
+      </c>
+      <c r="C89" s="53" t="n"/>
+      <c r="D89" s="53" t="n"/>
+      <c r="E89" s="53" t="n"/>
+      <c r="F89" s="53" t="n"/>
+      <c r="G89" s="53" t="n"/>
+      <c r="H89" s="53" t="n"/>
+      <c r="I89" s="53" t="n"/>
+      <c r="J89" s="53" t="n"/>
+      <c r="K89" s="53" t="n"/>
+      <c r="L89" s="53" t="n"/>
+      <c r="M89" s="53" t="n"/>
+      <c r="N89" s="53" t="n"/>
+      <c r="O89" s="54" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="37" t="inlineStr">
@@ -8192,15 +8264,28 @@
       </c>
       <c r="B149" s="31" t="inlineStr">
         <is>
-          <t>Koordinatlar: 41.0082° K, 28.9784° D
-🚇 Metro A İstasyonu — 350m
-🚇 Metro B İstasyonu — 800m
-🏫 İlköğretim Okulu — 450m
-🏥 Devlet Hastanesi — 1.2 km
-🛒 Alışveriş Merkezi — 600m
-🌳 Kent Parkı — 200m</t>
-        </is>
-      </c>
+          <t>**Koordinatlar:** 41.0082° K, 28.9784° D
+🚇 Metro A İstasyonu — **350m**
+🚇 Metro B İstasyonu — **800m**
+🏫 İlköğretim Okulu — **450m**
+🏥 Devlet Hastanesi — **1.2 km**
+🛒 Alışveriş Merkezi — **600m**
+🌳 Kent Parkı — **200m**</t>
+        </is>
+      </c>
+      <c r="C149" s="53" t="n"/>
+      <c r="D149" s="53" t="n"/>
+      <c r="E149" s="53" t="n"/>
+      <c r="F149" s="53" t="n"/>
+      <c r="G149" s="53" t="n"/>
+      <c r="H149" s="53" t="n"/>
+      <c r="I149" s="53" t="n"/>
+      <c r="J149" s="53" t="n"/>
+      <c r="K149" s="53" t="n"/>
+      <c r="L149" s="53" t="n"/>
+      <c r="M149" s="53" t="n"/>
+      <c r="N149" s="53" t="n"/>
+      <c r="O149" s="54" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="32" t="inlineStr">
@@ -9020,13 +9105,28 @@
       </c>
       <c r="B164" s="36" t="inlineStr">
         <is>
-          <t>Geliştirici: VEA Development A.Ş.
-4 Blok | 240 Daire | 1+1 / 2+1 / 3+1
-Teslim: Aralık 2026
+          <t>**Geliştirici:** VEA Development A.Ş.
+**Blok Sayısı:** 4 Blok
+**Toplam Ünite:** 240 Daire
+**Kat Aralığı:** 1+1 / 2+1 / 3+1
+**Teslim Tarihi:** Aralık 2026
 🏅 LEED Gold Sertifikası
 🌱 Enerji Sınıfı: A+</t>
         </is>
       </c>
+      <c r="C164" s="53" t="n"/>
+      <c r="D164" s="53" t="n"/>
+      <c r="E164" s="53" t="n"/>
+      <c r="F164" s="53" t="n"/>
+      <c r="G164" s="53" t="n"/>
+      <c r="H164" s="53" t="n"/>
+      <c r="I164" s="53" t="n"/>
+      <c r="J164" s="53" t="n"/>
+      <c r="K164" s="53" t="n"/>
+      <c r="L164" s="53" t="n"/>
+      <c r="M164" s="53" t="n"/>
+      <c r="N164" s="53" t="n"/>
+      <c r="O164" s="54" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="37" t="inlineStr">
@@ -9846,15 +9946,28 @@
       </c>
       <c r="B179" s="31" t="inlineStr">
         <is>
-          <t>🚇 M3 Metro Hattı — 350m
-🚌 Otobüs Durağı — 120m
-🚖 Taksi Durağı — 80m
-🛵 Bisiklet Yolu — Proje önünden
-Havalimanı: 28 dk (E80)
-Boğaz Köprüsü: 12 dk
-TEM Bağlantısı: 5 dk</t>
-        </is>
-      </c>
+          <t>🚇 M3 Metro Hattı — **350m**
+🚌 Otobüs Durağı — **120m**
+🚖 Taksi Durağı — **80m**
+🛵 Bisiklet Yolu — **Proje önünden geçiyor**
+**Havalimanı:** 28 dk (E80)
+**Boğaz Köprüsü:** 12 dk
+**TEM Bağlantısı:** 5 dk</t>
+        </is>
+      </c>
+      <c r="C179" s="53" t="n"/>
+      <c r="D179" s="53" t="n"/>
+      <c r="E179" s="53" t="n"/>
+      <c r="F179" s="53" t="n"/>
+      <c r="G179" s="53" t="n"/>
+      <c r="H179" s="53" t="n"/>
+      <c r="I179" s="53" t="n"/>
+      <c r="J179" s="53" t="n"/>
+      <c r="K179" s="53" t="n"/>
+      <c r="L179" s="53" t="n"/>
+      <c r="M179" s="53" t="n"/>
+      <c r="N179" s="53" t="n"/>
+      <c r="O179" s="54" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
@@ -10674,12 +10787,26 @@
       </c>
       <c r="B194" s="36" t="inlineStr">
         <is>
-          <t>Walk Score®: 9.2 / 10
-🚶 Yürünebilirlik: Mükemmel
-🚲 Bisiklet Dostu: İyi
-🚇 Toplu Ulaşım: Çok İyi</t>
-        </is>
-      </c>
+          <t>**9.2** / 10
+Walk Score® Değerlendirmesi
+🚶 Yürünebilirlik: **Mükemmel**
+🚲 Bisiklet Dostu: **İyi**
+🚇 Toplu Ulaşım: **Çok İyi**</t>
+        </is>
+      </c>
+      <c r="C194" s="53" t="n"/>
+      <c r="D194" s="53" t="n"/>
+      <c r="E194" s="53" t="n"/>
+      <c r="F194" s="53" t="n"/>
+      <c r="G194" s="53" t="n"/>
+      <c r="H194" s="53" t="n"/>
+      <c r="I194" s="53" t="n"/>
+      <c r="J194" s="53" t="n"/>
+      <c r="K194" s="53" t="n"/>
+      <c r="L194" s="53" t="n"/>
+      <c r="M194" s="53" t="n"/>
+      <c r="N194" s="53" t="n"/>
+      <c r="O194" s="54" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="37" t="inlineStr">
@@ -11499,13 +11626,26 @@
       </c>
       <c r="B209" s="31" t="inlineStr">
         <is>
-          <t>1+1 — 55–65 m² — 68 Daire
-2+1 — 85–100 m² — 120 Daire
-3+1 — 130–155 m² — 52 Daire
+          <t>**1+1** — 55–65 m² — 68 Daire
+**2+1** — 85–100 m² — 120 Daire
+**3+1** — 130–155 m² — 52 Daire
 ✅ Tüm üniteler güney-doğu cepheli
 ✅ Panoramik balkon her dairede</t>
         </is>
       </c>
+      <c r="C209" s="53" t="n"/>
+      <c r="D209" s="53" t="n"/>
+      <c r="E209" s="53" t="n"/>
+      <c r="F209" s="53" t="n"/>
+      <c r="G209" s="53" t="n"/>
+      <c r="H209" s="53" t="n"/>
+      <c r="I209" s="53" t="n"/>
+      <c r="J209" s="53" t="n"/>
+      <c r="K209" s="53" t="n"/>
+      <c r="L209" s="53" t="n"/>
+      <c r="M209" s="53" t="n"/>
+      <c r="N209" s="53" t="n"/>
+      <c r="O209" s="54" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="32" t="inlineStr">
@@ -12325,12 +12465,25 @@
       </c>
       <c r="B224" s="36" t="inlineStr">
         <is>
-          <t>1+1 — 2.850.000 ₺'den başlayan
-2+1 — 4.200.000 ₺'den başlayan
-3+1 — 6.500.000 ₺'den başlayan
+          <t>**1+1** — 2.850.000 ₺'den başlayan
+**2+1** — 4.200.000 ₺'den başlayan
+**3+1** — 6.500.000 ₺'den başlayan
 * Fiyatlar piyasa koşullarına göre değişkenlik gösterebilir.</t>
         </is>
       </c>
+      <c r="C224" s="53" t="n"/>
+      <c r="D224" s="53" t="n"/>
+      <c r="E224" s="53" t="n"/>
+      <c r="F224" s="53" t="n"/>
+      <c r="G224" s="53" t="n"/>
+      <c r="H224" s="53" t="n"/>
+      <c r="I224" s="53" t="n"/>
+      <c r="J224" s="53" t="n"/>
+      <c r="K224" s="53" t="n"/>
+      <c r="L224" s="53" t="n"/>
+      <c r="M224" s="53" t="n"/>
+      <c r="N224" s="53" t="n"/>
+      <c r="O224" s="54" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="37" t="inlineStr">
@@ -15359,6 +15512,19 @@
 Bina Yüksekliği: 14 kat</t>
         </is>
       </c>
+      <c r="C285" s="53" t="n"/>
+      <c r="D285" s="53" t="n"/>
+      <c r="E285" s="53" t="n"/>
+      <c r="F285" s="53" t="n"/>
+      <c r="G285" s="53" t="n"/>
+      <c r="H285" s="53" t="n"/>
+      <c r="I285" s="53" t="n"/>
+      <c r="J285" s="53" t="n"/>
+      <c r="K285" s="53" t="n"/>
+      <c r="L285" s="53" t="n"/>
+      <c r="M285" s="53" t="n"/>
+      <c r="N285" s="53" t="n"/>
+      <c r="O285" s="54" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="32" t="inlineStr">
@@ -16185,6 +16351,19 @@
 ⭐ En Çok Tercih Edilen Seçenek</t>
         </is>
       </c>
+      <c r="C300" s="53" t="n"/>
+      <c r="D300" s="53" t="n"/>
+      <c r="E300" s="53" t="n"/>
+      <c r="F300" s="53" t="n"/>
+      <c r="G300" s="53" t="n"/>
+      <c r="H300" s="53" t="n"/>
+      <c r="I300" s="53" t="n"/>
+      <c r="J300" s="53" t="n"/>
+      <c r="K300" s="53" t="n"/>
+      <c r="L300" s="53" t="n"/>
+      <c r="M300" s="53" t="n"/>
+      <c r="N300" s="53" t="n"/>
+      <c r="O300" s="54" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="37" t="inlineStr">
@@ -17011,6 +17190,19 @@
 Bina Yüksekliği: 14 kat</t>
         </is>
       </c>
+      <c r="C315" s="53" t="n"/>
+      <c r="D315" s="53" t="n"/>
+      <c r="E315" s="53" t="n"/>
+      <c r="F315" s="53" t="n"/>
+      <c r="G315" s="53" t="n"/>
+      <c r="H315" s="53" t="n"/>
+      <c r="I315" s="53" t="n"/>
+      <c r="J315" s="53" t="n"/>
+      <c r="K315" s="53" t="n"/>
+      <c r="L315" s="53" t="n"/>
+      <c r="M315" s="53" t="n"/>
+      <c r="N315" s="53" t="n"/>
+      <c r="O315" s="54" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="32" t="inlineStr">
@@ -17836,6 +18028,19 @@
 ✅ Değer artışı potansiyeli</t>
         </is>
       </c>
+      <c r="C330" s="53" t="n"/>
+      <c r="D330" s="53" t="n"/>
+      <c r="E330" s="53" t="n"/>
+      <c r="F330" s="53" t="n"/>
+      <c r="G330" s="53" t="n"/>
+      <c r="H330" s="53" t="n"/>
+      <c r="I330" s="53" t="n"/>
+      <c r="J330" s="53" t="n"/>
+      <c r="K330" s="53" t="n"/>
+      <c r="L330" s="53" t="n"/>
+      <c r="M330" s="53" t="n"/>
+      <c r="N330" s="53" t="n"/>
+      <c r="O330" s="54" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="37" t="inlineStr">
@@ -20663,6 +20868,19 @@
 Otopark: 480 araç kapasiteli</t>
         </is>
       </c>
+      <c r="C387" s="53" t="n"/>
+      <c r="D387" s="53" t="n"/>
+      <c r="E387" s="53" t="n"/>
+      <c r="F387" s="53" t="n"/>
+      <c r="G387" s="53" t="n"/>
+      <c r="H387" s="53" t="n"/>
+      <c r="I387" s="53" t="n"/>
+      <c r="J387" s="53" t="n"/>
+      <c r="K387" s="53" t="n"/>
+      <c r="L387" s="53" t="n"/>
+      <c r="M387" s="53" t="n"/>
+      <c r="N387" s="53" t="n"/>
+      <c r="O387" s="54" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="32" t="inlineStr">
@@ -21491,6 +21709,19 @@
 📦 Kargo Odası</t>
         </is>
       </c>
+      <c r="C402" s="53" t="n"/>
+      <c r="D402" s="53" t="n"/>
+      <c r="E402" s="53" t="n"/>
+      <c r="F402" s="53" t="n"/>
+      <c r="G402" s="53" t="n"/>
+      <c r="H402" s="53" t="n"/>
+      <c r="I402" s="53" t="n"/>
+      <c r="J402" s="53" t="n"/>
+      <c r="K402" s="53" t="n"/>
+      <c r="L402" s="53" t="n"/>
+      <c r="M402" s="53" t="n"/>
+      <c r="N402" s="53" t="n"/>
+      <c r="O402" s="54" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="37" t="inlineStr">
@@ -24430,6 +24661,19 @@
 ☀️ Günün 7 saati doğal ışık</t>
         </is>
       </c>
+      <c r="C463" s="53" t="n"/>
+      <c r="D463" s="53" t="n"/>
+      <c r="E463" s="53" t="n"/>
+      <c r="F463" s="53" t="n"/>
+      <c r="G463" s="53" t="n"/>
+      <c r="H463" s="53" t="n"/>
+      <c r="I463" s="53" t="n"/>
+      <c r="J463" s="53" t="n"/>
+      <c r="K463" s="53" t="n"/>
+      <c r="L463" s="53" t="n"/>
+      <c r="M463" s="53" t="n"/>
+      <c r="N463" s="53" t="n"/>
+      <c r="O463" s="54" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
       <c r="A464" s="32" t="inlineStr">
@@ -25256,6 +25500,19 @@
 * Aksesuarlar örnek gösterim amaçlıdır.</t>
         </is>
       </c>
+      <c r="C478" s="53" t="n"/>
+      <c r="D478" s="53" t="n"/>
+      <c r="E478" s="53" t="n"/>
+      <c r="F478" s="53" t="n"/>
+      <c r="G478" s="53" t="n"/>
+      <c r="H478" s="53" t="n"/>
+      <c r="I478" s="53" t="n"/>
+      <c r="J478" s="53" t="n"/>
+      <c r="K478" s="53" t="n"/>
+      <c r="L478" s="53" t="n"/>
+      <c r="M478" s="53" t="n"/>
+      <c r="N478" s="53" t="n"/>
+      <c r="O478" s="54" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
       <c r="A479" s="37" t="inlineStr">
@@ -26082,6 +26339,19 @@
 ✅ Ankastre cihazlar dahil</t>
         </is>
       </c>
+      <c r="C493" s="53" t="n"/>
+      <c r="D493" s="53" t="n"/>
+      <c r="E493" s="53" t="n"/>
+      <c r="F493" s="53" t="n"/>
+      <c r="G493" s="53" t="n"/>
+      <c r="H493" s="53" t="n"/>
+      <c r="I493" s="53" t="n"/>
+      <c r="J493" s="53" t="n"/>
+      <c r="K493" s="53" t="n"/>
+      <c r="L493" s="53" t="n"/>
+      <c r="M493" s="53" t="n"/>
+      <c r="N493" s="53" t="n"/>
+      <c r="O493" s="54" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
       <c r="A494" s="32" t="inlineStr">
@@ -26907,6 +27177,19 @@
 🔧 Buzdolabı: Samsung French Door</t>
         </is>
       </c>
+      <c r="C508" s="53" t="n"/>
+      <c r="D508" s="53" t="n"/>
+      <c r="E508" s="53" t="n"/>
+      <c r="F508" s="53" t="n"/>
+      <c r="G508" s="53" t="n"/>
+      <c r="H508" s="53" t="n"/>
+      <c r="I508" s="53" t="n"/>
+      <c r="J508" s="53" t="n"/>
+      <c r="K508" s="53" t="n"/>
+      <c r="L508" s="53" t="n"/>
+      <c r="M508" s="53" t="n"/>
+      <c r="N508" s="53" t="n"/>
+      <c r="O508" s="54" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1">
       <c r="A509" s="37" t="inlineStr">
@@ -27733,6 +28016,19 @@
 🌅 Sabah güneşi</t>
         </is>
       </c>
+      <c r="C523" s="53" t="n"/>
+      <c r="D523" s="53" t="n"/>
+      <c r="E523" s="53" t="n"/>
+      <c r="F523" s="53" t="n"/>
+      <c r="G523" s="53" t="n"/>
+      <c r="H523" s="53" t="n"/>
+      <c r="I523" s="53" t="n"/>
+      <c r="J523" s="53" t="n"/>
+      <c r="K523" s="53" t="n"/>
+      <c r="L523" s="53" t="n"/>
+      <c r="M523" s="53" t="n"/>
+      <c r="N523" s="53" t="n"/>
+      <c r="O523" s="54" t="n"/>
     </row>
     <row r="524" ht="18" customHeight="1">
       <c r="A524" s="32" t="inlineStr">
@@ -28558,6 +28854,19 @@
 ❄️ Daikin Inverter A++</t>
         </is>
       </c>
+      <c r="C538" s="53" t="n"/>
+      <c r="D538" s="53" t="n"/>
+      <c r="E538" s="53" t="n"/>
+      <c r="F538" s="53" t="n"/>
+      <c r="G538" s="53" t="n"/>
+      <c r="H538" s="53" t="n"/>
+      <c r="I538" s="53" t="n"/>
+      <c r="J538" s="53" t="n"/>
+      <c r="K538" s="53" t="n"/>
+      <c r="L538" s="53" t="n"/>
+      <c r="M538" s="53" t="n"/>
+      <c r="N538" s="53" t="n"/>
+      <c r="O538" s="54" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1">
       <c r="A539" s="37" t="inlineStr">
@@ -29384,6 +29693,19 @@
 ✅ Yerden ısıtma sistemi</t>
         </is>
       </c>
+      <c r="C553" s="53" t="n"/>
+      <c r="D553" s="53" t="n"/>
+      <c r="E553" s="53" t="n"/>
+      <c r="F553" s="53" t="n"/>
+      <c r="G553" s="53" t="n"/>
+      <c r="H553" s="53" t="n"/>
+      <c r="I553" s="53" t="n"/>
+      <c r="J553" s="53" t="n"/>
+      <c r="K553" s="53" t="n"/>
+      <c r="L553" s="53" t="n"/>
+      <c r="M553" s="53" t="n"/>
+      <c r="N553" s="53" t="n"/>
+      <c r="O553" s="54" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1">
       <c r="A554" s="32" t="inlineStr">
@@ -30209,6 +30531,19 @@
 🔧 Batarya: Hansgrohe Metris</t>
         </is>
       </c>
+      <c r="C568" s="53" t="n"/>
+      <c r="D568" s="53" t="n"/>
+      <c r="E568" s="53" t="n"/>
+      <c r="F568" s="53" t="n"/>
+      <c r="G568" s="53" t="n"/>
+      <c r="H568" s="53" t="n"/>
+      <c r="I568" s="53" t="n"/>
+      <c r="J568" s="53" t="n"/>
+      <c r="K568" s="53" t="n"/>
+      <c r="L568" s="53" t="n"/>
+      <c r="M568" s="53" t="n"/>
+      <c r="N568" s="53" t="n"/>
+      <c r="O568" s="54" t="n"/>
     </row>
     <row r="569" ht="18" customHeight="1">
       <c r="A569" s="37" t="inlineStr">
@@ -31033,6 +31368,19 @@
 Pencere: Güney Yönü</t>
         </is>
       </c>
+      <c r="C583" s="53" t="n"/>
+      <c r="D583" s="53" t="n"/>
+      <c r="E583" s="53" t="n"/>
+      <c r="F583" s="53" t="n"/>
+      <c r="G583" s="53" t="n"/>
+      <c r="H583" s="53" t="n"/>
+      <c r="I583" s="53" t="n"/>
+      <c r="J583" s="53" t="n"/>
+      <c r="K583" s="53" t="n"/>
+      <c r="L583" s="53" t="n"/>
+      <c r="M583" s="53" t="n"/>
+      <c r="N583" s="53" t="n"/>
+      <c r="O583" s="54" t="n"/>
     </row>
     <row r="584" ht="18" customHeight="1">
       <c r="A584" s="32" t="inlineStr">
@@ -31857,6 +32205,19 @@
 8cm XPS Isı Yalıtımı</t>
         </is>
       </c>
+      <c r="C598" s="53" t="n"/>
+      <c r="D598" s="53" t="n"/>
+      <c r="E598" s="53" t="n"/>
+      <c r="F598" s="53" t="n"/>
+      <c r="G598" s="53" t="n"/>
+      <c r="H598" s="53" t="n"/>
+      <c r="I598" s="53" t="n"/>
+      <c r="J598" s="53" t="n"/>
+      <c r="K598" s="53" t="n"/>
+      <c r="L598" s="53" t="n"/>
+      <c r="M598" s="53" t="n"/>
+      <c r="N598" s="53" t="n"/>
+      <c r="O598" s="54" t="n"/>
     </row>
     <row r="599" ht="18" customHeight="1">
       <c r="A599" s="37" t="inlineStr">
@@ -32682,6 +33043,19 @@
 ✅ Pencereli — doğal havalandırma</t>
         </is>
       </c>
+      <c r="C613" s="53" t="n"/>
+      <c r="D613" s="53" t="n"/>
+      <c r="E613" s="53" t="n"/>
+      <c r="F613" s="53" t="n"/>
+      <c r="G613" s="53" t="n"/>
+      <c r="H613" s="53" t="n"/>
+      <c r="I613" s="53" t="n"/>
+      <c r="J613" s="53" t="n"/>
+      <c r="K613" s="53" t="n"/>
+      <c r="L613" s="53" t="n"/>
+      <c r="M613" s="53" t="n"/>
+      <c r="N613" s="53" t="n"/>
+      <c r="O613" s="54" t="n"/>
     </row>
     <row r="614" ht="18" customHeight="1">
       <c r="A614" s="32" t="inlineStr">
@@ -33507,6 +33881,19 @@
 🔧 Batarya: Grohe Eurosmart</t>
         </is>
       </c>
+      <c r="C628" s="53" t="n"/>
+      <c r="D628" s="53" t="n"/>
+      <c r="E628" s="53" t="n"/>
+      <c r="F628" s="53" t="n"/>
+      <c r="G628" s="53" t="n"/>
+      <c r="H628" s="53" t="n"/>
+      <c r="I628" s="53" t="n"/>
+      <c r="J628" s="53" t="n"/>
+      <c r="K628" s="53" t="n"/>
+      <c r="L628" s="53" t="n"/>
+      <c r="M628" s="53" t="n"/>
+      <c r="N628" s="53" t="n"/>
+      <c r="O628" s="54" t="n"/>
     </row>
     <row r="629" ht="18" customHeight="1">
       <c r="A629" s="37" t="inlineStr">
@@ -36330,6 +36717,19 @@
 📱 Mobil: Joystick ile kontrol</t>
         </is>
       </c>
+      <c r="C685" s="53" t="n"/>
+      <c r="D685" s="53" t="n"/>
+      <c r="E685" s="53" t="n"/>
+      <c r="F685" s="53" t="n"/>
+      <c r="G685" s="53" t="n"/>
+      <c r="H685" s="53" t="n"/>
+      <c r="I685" s="53" t="n"/>
+      <c r="J685" s="53" t="n"/>
+      <c r="K685" s="53" t="n"/>
+      <c r="L685" s="53" t="n"/>
+      <c r="M685" s="53" t="n"/>
+      <c r="N685" s="53" t="n"/>
+      <c r="O685" s="54" t="n"/>
     </row>
     <row r="686" ht="18" customHeight="1">
       <c r="A686" s="32" t="inlineStr">
@@ -37156,6 +37556,19 @@
 VR kulaklık bağlıysa: Enter VR seçin</t>
         </is>
       </c>
+      <c r="C700" s="53" t="n"/>
+      <c r="D700" s="53" t="n"/>
+      <c r="E700" s="53" t="n"/>
+      <c r="F700" s="53" t="n"/>
+      <c r="G700" s="53" t="n"/>
+      <c r="H700" s="53" t="n"/>
+      <c r="I700" s="53" t="n"/>
+      <c r="J700" s="53" t="n"/>
+      <c r="K700" s="53" t="n"/>
+      <c r="L700" s="53" t="n"/>
+      <c r="M700" s="53" t="n"/>
+      <c r="N700" s="53" t="n"/>
+      <c r="O700" s="54" t="n"/>
     </row>
     <row r="701" ht="18" customHeight="1">
       <c r="A701" s="37" t="inlineStr">

--- a/demo2/demo2-input_2.xlsx
+++ b/demo2/demo2-input_2.xlsx
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>Asset satır 9</t>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-opt-v2.glb</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C44" s="22" t="inlineStr">
         <is>
-          <t>Asset satır 13</t>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2kopuk-normalfacade-opt-v5.glb</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C115" s="22" t="inlineStr">
         <is>
-          <t>Asset satır 9</t>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-opt-v2.glb</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C116" s="22" t="inlineStr">
         <is>
-          <t>Asset satır 13</t>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2kopuk-normalfacade-opt-v5.glb</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
